--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF7E754-9EEA-42C5-8672-674C40F9D8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3214E9D8-C187-49E0-9DC7-D23E92FB022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="88">
   <si>
     <t>Client</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>James Craven</t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -696,7 +699,6 @@
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1020,37 +1022,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1246,7 +1248,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1344,7 +1346,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1442,7 +1444,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1540,14 +1542,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" t="s">
         <v>62</v>
       </c>
       <c r="D6" t="s">
@@ -1638,7 +1640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1736,14 +1738,14 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
@@ -1834,14 +1836,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" t="s">
         <v>65</v>
       </c>
       <c r="D9" t="s">
@@ -1941,27 +1943,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1973,14 +1981,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1993,17 +2001,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -2016,17 +2024,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,7 +2060,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -2087,14 +2095,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -2108,7 +2116,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>70</v>
       </c>
@@ -2122,7 +2130,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>70</v>
       </c>
@@ -2136,7 +2144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>70</v>
       </c>
@@ -2150,7 +2158,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>70</v>
       </c>
@@ -2164,7 +2172,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>70</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>70</v>
       </c>
@@ -2192,7 +2200,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2206,7 +2214,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>70</v>
       </c>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3214E9D8-C187-49E0-9DC7-D23E92FB022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE7FF14-2EC9-4393-818E-BF009D568736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -1075,863 +1075,863 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
-        <v>73</v>
-      </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
         <v>74</v>
       </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="O3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L3" t="s">
+      <c r="U3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" t="s">
         <v>72</v>
       </c>
-      <c r="M3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="W3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="s">
         <v>75</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U3" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="O4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U4" t="s">
+        <v>28</v>
+      </c>
+      <c r="V4" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" t="s">
+        <v>31</v>
+      </c>
+      <c r="X4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="s">
         <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" t="s">
-        <v>75</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V4" t="s">
-        <v>73</v>
-      </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="s">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="O5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L5" t="s">
+      <c r="U5" t="s">
+        <v>28</v>
+      </c>
+      <c r="V5" t="s">
         <v>72</v>
       </c>
-      <c r="M5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="W5" t="s">
+        <v>31</v>
+      </c>
+      <c r="X5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF5" t="s">
         <v>75</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V5" t="s">
-        <v>73</v>
-      </c>
-      <c r="W5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="O6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U6" t="s">
+        <v>28</v>
+      </c>
+      <c r="V6" t="s">
+        <v>72</v>
+      </c>
+      <c r="W6" t="s">
+        <v>31</v>
+      </c>
+      <c r="X6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="s">
         <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U6" t="s">
-        <v>29</v>
-      </c>
-      <c r="V6" t="s">
-        <v>73</v>
-      </c>
-      <c r="W6" t="s">
-        <v>32</v>
-      </c>
-      <c r="X6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="s">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="O7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L7" t="s">
+      <c r="U7" t="s">
+        <v>28</v>
+      </c>
+      <c r="V7" t="s">
         <v>72</v>
       </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="W7" t="s">
+        <v>31</v>
+      </c>
+      <c r="X7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF7" t="s">
         <v>75</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R7" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" t="s">
-        <v>26</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U7" t="s">
-        <v>29</v>
-      </c>
-      <c r="V7" t="s">
-        <v>73</v>
-      </c>
-      <c r="W7" t="s">
-        <v>32</v>
-      </c>
-      <c r="X7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="O8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U8" t="s">
+        <v>28</v>
+      </c>
+      <c r="V8" t="s">
+        <v>72</v>
+      </c>
+      <c r="W8" t="s">
+        <v>31</v>
+      </c>
+      <c r="X8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF8" t="s">
         <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" t="s">
-        <v>84</v>
-      </c>
-      <c r="L8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S8" t="s">
-        <v>26</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U8" t="s">
-        <v>29</v>
-      </c>
-      <c r="V8" t="s">
-        <v>73</v>
-      </c>
-      <c r="W8" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" t="s">
         <v>74</v>
       </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="O9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" t="s">
+        <v>25</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L9" t="s">
+      <c r="U9" t="s">
+        <v>28</v>
+      </c>
+      <c r="V9" t="s">
         <v>72</v>
       </c>
-      <c r="M9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="W9" t="s">
+        <v>31</v>
+      </c>
+      <c r="X9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF9" t="s">
         <v>75</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R9" t="s">
-        <v>26</v>
-      </c>
-      <c r="S9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="U9" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9" t="s">
-        <v>73</v>
-      </c>
-      <c r="W9" t="s">
-        <v>32</v>
-      </c>
-      <c r="X9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1952,24 +1952,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1985,12 +1985,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2008,12 +2008,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2036,54 +2036,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2104,128 +2104,128 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
         <v>71</v>
       </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" t="s">
         <v>71</v>
       </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" t="s">
         <v>71</v>
       </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE7FF14-2EC9-4393-818E-BF009D568736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A35045-FFC2-4746-8174-35836DD7418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="87">
   <si>
     <t>Client</t>
   </si>
@@ -288,9 +288,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>James Craven</t>
   </si>
   <si>
     <t>Business Services</t>
@@ -1161,7 +1158,7 @@
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1259,7 +1256,7 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1357,7 +1354,7 @@
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1455,7 +1452,7 @@
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -1553,7 +1550,7 @@
         <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -1651,7 +1648,7 @@
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -1749,7 +1746,7 @@
         <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -1847,7 +1844,7 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -1948,6 +1945,7 @@
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1963,7 +1961,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
         <v>82</v>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A35045-FFC2-4746-8174-35836DD7418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7EA8F5-7562-4E9E-97F0-6C9EB15D943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="88">
   <si>
     <t>Client</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Chris1 Lord1</t>
   </si>
 </sst>
 </file>
@@ -2060,7 +2063,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7EA8F5-7562-4E9E-97F0-6C9EB15D943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F02274-6930-45C2-824C-03C105F0E6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="89">
   <si>
     <t>Client</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>Chris1 Lord1</t>
+  </si>
+  <si>
+    <t>Andy Chen</t>
   </si>
 </sst>
 </file>
@@ -1022,37 +1025,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>85</v>
@@ -1248,7 +1251,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1289,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>85</v>
@@ -1346,7 +1349,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>16</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>85</v>
@@ -1444,7 +1447,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>16</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>85</v>
@@ -1542,7 +1545,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1583,7 +1586,7 @@
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>85</v>
@@ -1640,7 +1643,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1681,7 +1684,7 @@
         <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>85</v>
@@ -1738,7 +1741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>85</v>
@@ -1836,7 +1839,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -1877,7 +1880,7 @@
         <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>85</v>
@@ -1944,14 +1947,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -1982,14 +1985,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -2002,17 +2005,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -2025,17 +2028,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -2096,14 +2099,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2117,7 +2120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
@@ -2131,7 +2134,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>69</v>
       </c>
@@ -2145,7 +2148,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>69</v>
       </c>
@@ -2159,7 +2162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>69</v>
       </c>
@@ -2173,7 +2176,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>69</v>
       </c>
@@ -2187,7 +2190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>69</v>
       </c>
@@ -2201,7 +2204,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>69</v>
       </c>
@@ -2215,7 +2218,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>69</v>
       </c>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F02274-6930-45C2-824C-03C105F0E6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96F4734-0EB5-41DC-8485-2D5AD22CAC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1039,11 +1039,13 @@
     <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96F4734-0EB5-41DC-8485-2D5AD22CAC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EC4FBA-7F4A-46BF-A2A4-D73CB627B683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="89">
   <si>
     <t>Client</t>
   </si>
@@ -1024,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -1162,8 +1162,8 @@
       <c r="B2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>57</v>
+      <c r="C2" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="D2" t="s">
         <v>86</v>
@@ -1250,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="AF2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
@@ -1260,8 +1260,8 @@
       <c r="B3" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>58</v>
+      <c r="C3" t="s">
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>86</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="AF3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
@@ -1359,7 +1359,7 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>86</v>
@@ -1446,7 +1446,7 @@
         <v>8</v>
       </c>
       <c r="AF4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
@@ -1457,7 +1457,7 @@
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
         <v>86</v>
@@ -1544,7 +1544,7 @@
         <v>8</v>
       </c>
       <c r="AF5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
@@ -1555,7 +1555,7 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
         <v>86</v>
@@ -1642,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="AF6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
@@ -1653,7 +1653,7 @@
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -1740,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="AF7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
@@ -1751,7 +1751,7 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>86</v>
@@ -1838,104 +1838,6 @@
         <v>8</v>
       </c>
       <c r="AF8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>88</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R9" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" t="s">
-        <v>25</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U9" t="s">
-        <v>28</v>
-      </c>
-      <c r="V9" t="s">
-        <v>72</v>
-      </c>
-      <c r="W9" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF9" t="s">
         <v>75</v>
       </c>
     </row>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EC4FBA-7F4A-46BF-A2A4-D73CB627B683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B3E218-79E0-422D-B010-88D242D24DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -290,13 +287,16 @@
     <t>10</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Chris1 Lord1</t>
   </si>
   <si>
     <t>Andy Chen</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -1068,777 +1068,777 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
         <v>86</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L2" t="s">
+      <c r="U2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" t="s">
         <v>71</v>
       </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" t="s">
-        <v>88</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" t="s">
-        <v>72</v>
-      </c>
       <c r="W2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AC2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AD2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U3" t="s">
+        <v>27</v>
+      </c>
+      <c r="V3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF3" t="s">
         <v>73</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" t="s">
-        <v>25</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" t="s">
-        <v>72</v>
-      </c>
-      <c r="W3" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
         <v>86</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="O4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L4" t="s">
+      <c r="U4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" t="s">
         <v>71</v>
       </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" t="s">
-        <v>25</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V4" t="s">
-        <v>72</v>
-      </c>
       <c r="W4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AC4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AD4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" t="s">
+        <v>71</v>
+      </c>
+      <c r="W5" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="s">
         <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" t="s">
-        <v>88</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R5" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" t="s">
-        <v>25</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V5" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" t="s">
-        <v>31</v>
-      </c>
-      <c r="X5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" t="s">
         <v>86</v>
       </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="O6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L6" t="s">
+      <c r="U6" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" t="s">
         <v>71</v>
       </c>
-      <c r="M6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" t="s">
-        <v>25</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" t="s">
-        <v>28</v>
-      </c>
-      <c r="V6" t="s">
-        <v>72</v>
-      </c>
       <c r="W6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AC6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AD6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" t="s">
+        <v>71</v>
+      </c>
+      <c r="W7" t="s">
+        <v>30</v>
+      </c>
+      <c r="X7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" t="s">
-        <v>25</v>
-      </c>
-      <c r="S7" t="s">
-        <v>25</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U7" t="s">
-        <v>28</v>
-      </c>
-      <c r="V7" t="s">
-        <v>72</v>
-      </c>
-      <c r="W7" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" t="s">
         <v>86</v>
       </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="O8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L8" t="s">
+      <c r="U8" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" t="s">
         <v>71</v>
       </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" t="s">
-        <v>25</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U8" t="s">
-        <v>28</v>
-      </c>
-      <c r="V8" t="s">
-        <v>72</v>
-      </c>
       <c r="W8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AC8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AD8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1860,24 +1860,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
         <v>81</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1893,12 +1893,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1916,12 +1916,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1944,54 +1944,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2012,128 +2012,128 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" t="s">
         <v>70</v>
       </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
         <v>70</v>
       </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" t="s">
         <v>70</v>
       </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" t="s">
         <v>70</v>
       </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B3E218-79E0-422D-B010-88D242D24DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A16F20D-402E-43A3-90E6-D91C97DFBEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="88">
   <si>
     <t>Client</t>
   </si>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>Chris1 Lord1</t>
   </si>
   <si>
     <t>Andy Chen</t>
@@ -1068,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1166,7 +1163,7 @@
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1196,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>84</v>
@@ -1264,7 +1261,7 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1294,7 +1291,7 @@
         <v>15</v>
       </c>
       <c r="N3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>84</v>
@@ -1362,7 +1359,7 @@
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1392,7 +1389,7 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>84</v>
@@ -1460,7 +1457,7 @@
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -1490,7 +1487,7 @@
         <v>15</v>
       </c>
       <c r="N5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>84</v>
@@ -1558,7 +1555,7 @@
         <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -1588,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="N6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>84</v>
@@ -1656,7 +1653,7 @@
         <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -1686,7 +1683,7 @@
         <v>15</v>
       </c>
       <c r="N7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>84</v>
@@ -1754,7 +1751,7 @@
         <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -1784,7 +1781,7 @@
         <v>15</v>
       </c>
       <c r="N8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>84</v>
@@ -1970,7 +1967,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A16F20D-402E-43A3-90E6-D91C97DFBEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AF3F5E-A87D-41E9-943A-7615FA1D31DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AF3F5E-A87D-41E9-943A-7615FA1D31DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FFC7DE-FDB5-46C8-8505-0896AD068FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -294,6 +291,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -1022,39 +1022,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1077,765 +1077,765 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="V2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X2" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC2" t="s">
         <v>64</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="AD2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF3" t="s">
         <v>72</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
         <v>87</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="L2" t="s">
+      <c r="U6" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" t="s">
         <v>70</v>
       </c>
-      <c r="M2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="W6" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L7" t="s">
+        <v>69</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" t="s">
         <v>84</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="O7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" t="s">
         <v>84</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="O8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="U8" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W8" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AC8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" t="s">
-        <v>82</v>
-      </c>
-      <c r="L4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" t="s">
-        <v>85</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" t="s">
-        <v>71</v>
-      </c>
-      <c r="W4" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" t="s">
-        <v>70</v>
-      </c>
-      <c r="M5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" t="s">
-        <v>85</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U5" t="s">
-        <v>27</v>
-      </c>
-      <c r="V5" t="s">
-        <v>71</v>
-      </c>
-      <c r="W5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L6" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" t="s">
-        <v>24</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U6" t="s">
-        <v>27</v>
-      </c>
-      <c r="V6" t="s">
-        <v>71</v>
-      </c>
-      <c r="W6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L7" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" t="s">
-        <v>85</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S7" t="s">
-        <v>24</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U7" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7" t="s">
-        <v>71</v>
-      </c>
-      <c r="W7" t="s">
-        <v>30</v>
-      </c>
-      <c r="X7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" t="s">
-        <v>85</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U8" t="s">
-        <v>27</v>
-      </c>
-      <c r="V8" t="s">
-        <v>71</v>
-      </c>
-      <c r="W8" t="s">
-        <v>30</v>
-      </c>
-      <c r="X8" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1848,33 +1848,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
         <v>80</v>
       </c>
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1886,16 +1886,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1906,19 +1906,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1929,66 +1929,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2000,137 +2000,137 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
       <c r="D2" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C7" t="s">
         <v>69</v>
       </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C9" t="s">
         <v>69</v>
       </c>
-      <c r="C8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418FDF13-D72A-460B-808E-BFE432FF0973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39372AE4-CF94-466C-A891-E1457481499F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
     <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AppName" sheetId="5" r:id="rId3"/>
-    <sheet name="ModuleName" sheetId="6" r:id="rId4"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
-    <sheet name="Engagement" sheetId="4" r:id="rId6"/>
+    <sheet name="CAOUser" sheetId="8" r:id="rId3"/>
+    <sheet name="AppName" sheetId="5" r:id="rId4"/>
+    <sheet name="ModuleName" sheetId="6" r:id="rId5"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId6"/>
+    <sheet name="Engagement" sheetId="4" r:id="rId7"/>
+    <sheet name="Notes" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="97">
   <si>
     <t>Client</t>
   </si>
@@ -297,6 +299,30 @@
   </si>
   <si>
     <t>Engagements</t>
+  </si>
+  <si>
+    <t>Lorriane Johnson</t>
+  </si>
+  <si>
+    <t>Compliance User</t>
+  </si>
+  <si>
+    <t>Christine Sha</t>
+  </si>
+  <si>
+    <t>Legal User</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Legal Hold test Notes</t>
   </si>
 </sst>
 </file>
@@ -1887,6 +1913,43 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1906,7 +1969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1934,7 +1997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2005,7 +2068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2145,4 +2208,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388A5FB4-80B0-4A36-B46C-8E2770C1F8E1}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39372AE4-CF94-466C-A891-E1457481499F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D1AAB3-F40D-4ED9-BAC0-54F116DCFA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="99">
   <si>
     <t>Client</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>Legal Hold test Notes</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
+  </si>
+  <si>
+    <t>System Admin</t>
   </si>
 </sst>
 </file>
@@ -1914,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
@@ -1942,6 +1948,14 @@
       </c>
       <c r="B3" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D1AAB3-F40D-4ED9-BAC0-54F116DCFA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAB4B98-4460-4A50-A0A4-D2A4CECCE770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="CAOUser" sheetId="8" r:id="rId3"/>
-    <sheet name="AppName" sheetId="5" r:id="rId4"/>
-    <sheet name="ModuleName" sheetId="6" r:id="rId5"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
+    <sheet name="CAOUser" sheetId="8" r:id="rId2"/>
+    <sheet name="AppName" sheetId="5" r:id="rId3"/>
+    <sheet name="ModuleName" sheetId="6" r:id="rId4"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId5"/>
     <sheet name="AddContact" sheetId="3" r:id="rId6"/>
     <sheet name="Engagement" sheetId="4" r:id="rId7"/>
     <sheet name="Notes" sheetId="7" r:id="rId8"/>
@@ -1055,41 +1055,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1285,7 +1416,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1383,7 +1514,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1481,7 +1612,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -1579,7 +1710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -1677,7 +1808,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -1775,7 +1906,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1880,151 +2011,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2085,14 +2085,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>67</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>67</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>67</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -2227,17 +2227,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388A5FB4-80B0-4A36-B46C-8E2770C1F8E1}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>96</v>
       </c>

--- a/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
+++ b/TestData/LV_T1624_OpportunityToEngagementConversionMappingForFRJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAB4B98-4460-4A50-A0A4-D2A4CECCE770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B63DC2-EF97-4A6C-9053-61565669D766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="95">
   <si>
     <t>Client</t>
   </si>
@@ -299,18 +299,6 @@
   </si>
   <si>
     <t>Engagements</t>
-  </si>
-  <si>
-    <t>Lorriane Johnson</t>
-  </si>
-  <si>
-    <t>Compliance User</t>
-  </si>
-  <si>
-    <t>Christine Sha</t>
-  </si>
-  <si>
-    <t>Legal User</t>
   </si>
   <si>
     <t>User</t>
@@ -1057,14 +1045,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1075,7 +1063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1094,42 +1082,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AA2166-0BC1-42EB-8C55-F0979EE9638D}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1140,14 +1112,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19F56F96-8E69-465C-AD2C-16F74E4333CC}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1160,22 +1132,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A82162-87C2-47FB-939D-25F1C99EC756}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -1188,39 +1160,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1416,7 +1388,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1514,7 +1486,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -1612,7 +1584,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -1710,7 +1682,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -1808,7 +1780,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -1906,7 +1878,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -2014,17 +1986,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -2050,7 +2022,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -2085,14 +2057,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2106,7 +2078,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>67</v>
       </c>
@@ -2120,7 +2092,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>67</v>
       </c>
@@ -2134,7 +2106,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>67</v>
       </c>
@@ -2148,7 +2120,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -2162,7 +2134,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
@@ -2176,7 +2148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
@@ -2190,7 +2162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>67</v>
       </c>
@@ -2204,7 +2176,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -2227,19 +2199,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388A5FB4-80B0-4A36-B46C-8E2770C1F8E1}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
